--- a/output/reports/cv_experiment_XGBoost_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_XGBoost_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.721395015716553</v>
+        <v>1.832290172576904</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999719520409902</v>
+        <v>0.9965068384805602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997619986534119</v>
+        <v>0.9981012350213448</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74530553817749</v>
+        <v>0.8587064421248826</v>
       </c>
       <c r="H2" t="n">
-        <v>1.336347937583923</v>
+        <v>0.5801936221432377</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.320969104766846</v>
+        <v>0.5191829204559326</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997135281562806</v>
+        <v>0.9973711609502469</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997619986534119</v>
+        <v>0.9981012350213448</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74530553817749</v>
+        <v>0.8587064421248826</v>
       </c>
       <c r="H3" t="n">
-        <v>1.336347937583923</v>
+        <v>0.5801936221432377</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.632920503616333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9997214376926422</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9997619986534119</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.74530553817749</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.336347937583923</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.948121786117554</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9997140924135844</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9997619986534119</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.74530553817749</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.336347937583923</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.721395015716553</v>
+        <v>1.832290172576904</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999719520409902</v>
+        <v>0.9965068384805602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997619986534119</v>
+        <v>0.9981012350213448</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74530553817749</v>
+        <v>0.8587064421248826</v>
       </c>
       <c r="H2" t="n">
-        <v>1.336347937583923</v>
+        <v>0.5801936221432377</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.320969104766846</v>
+        <v>0.5191829204559326</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997135281562806</v>
+        <v>0.9973711609502469</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997619986534119</v>
+        <v>0.9981012350213448</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74530553817749</v>
+        <v>0.8587064421248826</v>
       </c>
       <c r="H3" t="n">
-        <v>1.336347937583923</v>
+        <v>0.5801936221432377</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.632920503616333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9997214376926422</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9997619986534119</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.74530553817749</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.336347937583923</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.948121786117554</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9997140924135844</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9997619986534119</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.74530553817749</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.336347937583923</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_child_weight': 1, 'max_depth': 3, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 3, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
